--- a/project/data/raw/soybean_meal_2019-2025.xlsx
+++ b/project/data/raw/soybean_meal_2019-2025.xlsx
@@ -951,13 +951,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -29284,17 +29277,53 @@
       <c r="A1560" s="6">
         <v>45833</v>
       </c>
+      <c r="B1560" s="7">
+        <v>3031</v>
+      </c>
+      <c r="C1560" s="7">
+        <v>3037</v>
+      </c>
+      <c r="D1560" s="7">
+        <v>2988</v>
+      </c>
+      <c r="E1560" s="7">
+        <v>2993</v>
+      </c>
       <c r="F1560" s="7"/>
     </row>
     <row r="1561" spans="1:6">
       <c r="A1561" s="6">
         <v>45834</v>
       </c>
+      <c r="B1561" s="7">
+        <v>2986</v>
+      </c>
+      <c r="C1561" s="7">
+        <v>2988</v>
+      </c>
+      <c r="D1561" s="7">
+        <v>2921</v>
+      </c>
+      <c r="E1561" s="7">
+        <v>2936</v>
+      </c>
       <c r="F1561" s="7"/>
     </row>
     <row r="1562" spans="1:6">
       <c r="A1562" s="6">
         <v>45835</v>
+      </c>
+      <c r="B1562" s="7">
+        <v>2940</v>
+      </c>
+      <c r="C1562" s="7">
+        <v>2949</v>
+      </c>
+      <c r="D1562" s="7">
+        <v>2926</v>
+      </c>
+      <c r="E1562" s="7">
+        <v>2946</v>
       </c>
       <c r="F1562" s="7"/>
     </row>
